--- a/Raw Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/Validation(1.5)(3tendon).xlsx
+++ b/Raw Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/Validation(1.5)(3tendon).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4012" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C533A85C-50D4-44FA-8667-DAA200B55087}"/>
+  <xr:revisionPtr revIDLastSave="4034" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48F22E1-F31A-4947-B8D0-A7AA3DB9ABD6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="49">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -200,6 +200,15 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>distances from mean</t>
+  </si>
+  <si>
+    <t>RMSE</t>
   </si>
 </sst>
 </file>
@@ -913,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B763EDC-8536-442D-A8D3-F37978D4DE80}">
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -929,9 +938,8 @@
     <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2494,7 +2502,199 @@
     </row>
     <row r="19" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L19" s="12"/>
-      <c r="R19" s="20"/>
+      <c r="Q19" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="20">
+        <f>AVERAGE(R3:R17)</f>
+        <v>2.6140031809473264E-4</v>
+      </c>
+      <c r="S19" s="20">
+        <f t="shared" ref="S19:W19" si="9">AVERAGE(S3:S17)</f>
+        <v>5.1108843002978376E-2</v>
+      </c>
+      <c r="T19" s="20">
+        <f t="shared" si="9"/>
+        <v>-8.9669783975772438E-2</v>
+      </c>
+      <c r="U19" s="20">
+        <f t="shared" si="9"/>
+        <v>-0.38623502298085693</v>
+      </c>
+      <c r="V19" s="20">
+        <f t="shared" si="9"/>
+        <v>-0.49112637753374183</v>
+      </c>
+      <c r="W19" s="20">
+        <f t="shared" si="9"/>
+        <v>-0.31239943922305452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" t="s">
+        <v>47</v>
+      </c>
+      <c r="R21">
+        <f>SQRT(SUMXMY2(R3:W3,R$19:W$19))</f>
+        <v>0.83793695879436769</v>
+      </c>
+      <c r="T21">
+        <f>SQRT(SUMXMY2(S3:U3,S$19:U$19))</f>
+        <v>0.25656800953205411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <f t="shared" ref="R22:R39" si="10">SQRT(SUMXMY2(R4:W4,R$19:W$19))</f>
+        <v>0.63214672593098142</v>
+      </c>
+      <c r="T22">
+        <f t="shared" ref="T22:T35" si="11">SQRT(SUMXMY2(S4:U4,S$19:U$19))</f>
+        <v>0.38345069020158007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R23">
+        <f t="shared" si="10"/>
+        <v>0.62725002153599552</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="11"/>
+        <v>0.18963890967821623</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <f t="shared" si="10"/>
+        <v>0.63679977377095409</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="11"/>
+        <v>0.22914721026943269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R25">
+        <f t="shared" si="10"/>
+        <v>0.41709743262664534</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="11"/>
+        <v>0.1037297223076433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R26">
+        <f t="shared" si="10"/>
+        <v>0.46138504182566825</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="11"/>
+        <v>0.11679723066485016</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <f t="shared" si="10"/>
+        <v>0.42749547495999285</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="11"/>
+        <v>0.22131127406657836</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R28">
+        <f t="shared" si="10"/>
+        <v>0.44713920615866437</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="11"/>
+        <v>0.23516861157065752</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R29">
+        <f t="shared" si="10"/>
+        <v>0.16664560088185035</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="11"/>
+        <v>0.12011116574896684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R30">
+        <f t="shared" si="10"/>
+        <v>0.65586173570796957</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="11"/>
+        <v>0.50266591208021716</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R31">
+        <f t="shared" si="10"/>
+        <v>0.63854691832300681</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="11"/>
+        <v>0.30044171960315386</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <f t="shared" si="10"/>
+        <v>0.43376740916840367</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="11"/>
+        <v>0.11341186237514604</v>
+      </c>
+    </row>
+    <row r="33" spans="17:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R33">
+        <f t="shared" si="10"/>
+        <v>0.13650005338613536</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="11"/>
+        <v>0.13571780084575144</v>
+      </c>
+    </row>
+    <row r="34" spans="17:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <f t="shared" si="10"/>
+        <v>0.86613066730103605</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="11"/>
+        <v>0.20738523318581112</v>
+      </c>
+    </row>
+    <row r="35" spans="17:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R35">
+        <f t="shared" si="10"/>
+        <v>0.41509170504221699</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="11"/>
+        <v>0.31854758178084619</v>
+      </c>
+    </row>
+    <row r="37" spans="17:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q37" t="s">
+        <v>48</v>
+      </c>
+      <c r="R37" cm="1">
+        <f t="array" ref="R37">SQRT(AVERAGE(R21:R35^2))</f>
+        <v>0.55768414436574965</v>
+      </c>
+      <c r="T37" cm="1">
+        <f t="array" ref="T37">SQRT(AVERAGE(T21:T35^2))</f>
+        <v>0.25339627024700967</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15044,11 +15244,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15305,27 +15506,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15350,9 +15541,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>